--- a/data/metadata/data_catalog.xlsx
+++ b/data/metadata/data_catalog.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\INSA_Lyon\2nd_semester\M1_Challenge_St_Exupery\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\INSA_Lyon\2nd_semester\M1_Challenge_St_Exupery\data\metadata\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="758" uniqueCount="299">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="759" uniqueCount="300">
   <si>
     <t>field name</t>
   </si>
@@ -932,6 +932,9 @@
   </si>
   <si>
     <t>Ask what is "Turn" in our context</t>
+  </si>
+  <si>
+    <t>Colonne1</t>
   </si>
 </sst>
 </file>
@@ -1045,7 +1048,24 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="8">
+  <dxfs count="9">
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="7"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
     <dxf>
       <font>
         <strike val="0"/>
@@ -1191,21 +1211,16 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Tableau2" displayName="Tableau2" ref="A1:F196" totalsRowShown="0" headerRowDxfId="7" dataDxfId="6">
-  <autoFilter ref="A1:F196">
-    <filterColumn colId="5">
-      <filters>
-        <filter val="1"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
-  <tableColumns count="6">
-    <tableColumn id="1" name="field name" dataDxfId="5"/>
-    <tableColumn id="2" name="mode" dataDxfId="4"/>
-    <tableColumn id="3" name="type" dataDxfId="3"/>
-    <tableColumn id="4" name="description" dataDxfId="2"/>
-    <tableColumn id="5" name="Questions / Remarks" dataDxfId="1"/>
-    <tableColumn id="6" name="Used on our model" dataDxfId="0"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Tableau2" displayName="Tableau2" ref="A1:G196" totalsRowShown="0" headerRowDxfId="8" dataDxfId="7">
+  <autoFilter ref="A1:G196"/>
+  <tableColumns count="7">
+    <tableColumn id="1" name="field name" dataDxfId="6"/>
+    <tableColumn id="2" name="mode" dataDxfId="5"/>
+    <tableColumn id="3" name="type" dataDxfId="4"/>
+    <tableColumn id="4" name="description" dataDxfId="3"/>
+    <tableColumn id="5" name="Questions / Remarks" dataDxfId="2"/>
+    <tableColumn id="7" name="Colonne1" dataDxfId="0"/>
+    <tableColumn id="6" name="Used on our model" dataDxfId="1"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1528,18 +1543,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I196"/>
+  <dimension ref="A1:J196"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="13.8"/>
   <cols>
     <col min="1" max="1" width="18.8984375" customWidth="1"/>
     <col min="4" max="4" width="25.296875" customWidth="1"/>
-    <col min="5" max="5" width="52.19921875" style="5" customWidth="1"/>
-    <col min="6" max="6" width="19.19921875" style="7" customWidth="1"/>
-    <col min="7" max="7" width="24.69921875" customWidth="1"/>
-    <col min="9" max="9" width="23" customWidth="1"/>
+    <col min="5" max="6" width="52.19921875" style="5" customWidth="1"/>
+    <col min="7" max="7" width="19.19921875" style="7" customWidth="1"/>
+    <col min="8" max="8" width="24.69921875" customWidth="1"/>
+    <col min="10" max="10" width="23" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" s="10" customFormat="1">
+    <row r="1" spans="1:10" s="10" customFormat="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1555,11 +1570,14 @@
       <c r="E1" s="9" t="s">
         <v>279</v>
       </c>
-      <c r="F1" s="7" t="s">
+      <c r="F1" s="9" t="s">
+        <v>299</v>
+      </c>
+      <c r="G1" s="7" t="s">
         <v>274</v>
       </c>
     </row>
-    <row r="2" spans="1:9" hidden="1">
+    <row r="2" spans="1:10">
       <c r="A2" s="2" t="s">
         <v>4</v>
       </c>
@@ -1572,11 +1590,14 @@
       <c r="D2" s="2" t="s">
         <v>207</v>
       </c>
-      <c r="F2" s="7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" hidden="1">
+      <c r="F2" s="5">
+        <v>0</v>
+      </c>
+      <c r="G2" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10">
       <c r="A3" s="2" t="s">
         <v>7</v>
       </c>
@@ -1589,17 +1610,20 @@
       <c r="D3" s="2" t="s">
         <v>207</v>
       </c>
-      <c r="F3" s="7">
-        <v>0</v>
-      </c>
-      <c r="H3">
-        <v>0</v>
-      </c>
-      <c r="I3" t="s">
+      <c r="F3" s="5">
+        <v>0</v>
+      </c>
+      <c r="G3" s="7">
+        <v>0</v>
+      </c>
+      <c r="I3">
+        <v>0</v>
+      </c>
+      <c r="J3" t="s">
         <v>281</v>
       </c>
     </row>
-    <row r="4" spans="1:9">
+    <row r="4" spans="1:10">
       <c r="A4" s="2" t="s">
         <v>9</v>
       </c>
@@ -1612,17 +1636,20 @@
       <c r="D4" s="2" t="s">
         <v>208</v>
       </c>
-      <c r="F4" s="7">
-        <v>1</v>
-      </c>
-      <c r="H4">
-        <v>1</v>
-      </c>
-      <c r="I4" t="s">
+      <c r="F4" s="5">
+        <v>1</v>
+      </c>
+      <c r="G4" s="7">
+        <v>1</v>
+      </c>
+      <c r="I4">
+        <v>1</v>
+      </c>
+      <c r="J4" t="s">
         <v>282</v>
       </c>
     </row>
-    <row r="5" spans="1:9" hidden="1">
+    <row r="5" spans="1:10">
       <c r="A5" s="2" t="s">
         <v>10</v>
       </c>
@@ -1636,17 +1663,20 @@
       <c r="E5" s="5" t="s">
         <v>285</v>
       </c>
-      <c r="F5" s="7">
-        <v>2</v>
-      </c>
-      <c r="H5">
-        <v>2</v>
-      </c>
-      <c r="I5" t="s">
+      <c r="F5" s="5">
+        <v>1</v>
+      </c>
+      <c r="G5" s="7">
+        <v>2</v>
+      </c>
+      <c r="I5">
+        <v>2</v>
+      </c>
+      <c r="J5" t="s">
         <v>283</v>
       </c>
     </row>
-    <row r="6" spans="1:9">
+    <row r="6" spans="1:10">
       <c r="A6" s="2" t="s">
         <v>11</v>
       </c>
@@ -1659,11 +1689,14 @@
       <c r="D6" s="2" t="s">
         <v>209</v>
       </c>
-      <c r="F6" s="7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9">
+      <c r="F6" s="5">
+        <v>0</v>
+      </c>
+      <c r="G6" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10">
       <c r="A7" s="2" t="s">
         <v>12</v>
       </c>
@@ -1679,11 +1712,14 @@
       <c r="E7" s="2" t="s">
         <v>270</v>
       </c>
-      <c r="F7" s="7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9">
+      <c r="F7" s="2">
+        <v>0</v>
+      </c>
+      <c r="G7" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10">
       <c r="A8" s="2" t="s">
         <v>13</v>
       </c>
@@ -1699,11 +1735,14 @@
       <c r="E8" s="6" t="s">
         <v>284</v>
       </c>
-      <c r="F8" s="7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9">
+      <c r="F8" s="6">
+        <v>1</v>
+      </c>
+      <c r="G8" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10">
       <c r="A9" s="2" t="s">
         <v>14</v>
       </c>
@@ -1716,11 +1755,14 @@
       <c r="D9" s="2" t="s">
         <v>212</v>
       </c>
-      <c r="F9" s="7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9">
+      <c r="F9" s="5">
+        <v>0</v>
+      </c>
+      <c r="G9" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10">
       <c r="A10" s="2" t="s">
         <v>15</v>
       </c>
@@ -1733,11 +1775,14 @@
       <c r="D10" s="2" t="s">
         <v>213</v>
       </c>
-      <c r="F10" s="7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9">
+      <c r="F10" s="5">
+        <v>1</v>
+      </c>
+      <c r="G10" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10">
       <c r="A11" s="2" t="s">
         <v>16</v>
       </c>
@@ -1753,11 +1798,14 @@
       <c r="E11" s="5" t="s">
         <v>280</v>
       </c>
-      <c r="F11" s="7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9">
+      <c r="F11" s="5">
+        <v>1</v>
+      </c>
+      <c r="G11" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10">
       <c r="A12" s="2" t="s">
         <v>17</v>
       </c>
@@ -1773,11 +1821,14 @@
       <c r="E12" s="5" t="s">
         <v>278</v>
       </c>
-      <c r="F12" s="7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9">
+      <c r="F12" s="5">
+        <v>1</v>
+      </c>
+      <c r="G12" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10">
       <c r="A13" s="2" t="s">
         <v>18</v>
       </c>
@@ -1793,11 +1844,14 @@
       <c r="E13" s="5" t="s">
         <v>286</v>
       </c>
-      <c r="F13" s="7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9">
+      <c r="F13" s="5">
+        <v>1</v>
+      </c>
+      <c r="G13" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10">
       <c r="A14" s="2" t="s">
         <v>19</v>
       </c>
@@ -1813,11 +1867,14 @@
       <c r="E14" s="5" t="s">
         <v>278</v>
       </c>
-      <c r="F14" s="7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9">
+      <c r="F14" s="5">
+        <v>0</v>
+      </c>
+      <c r="G14" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10">
       <c r="A15" s="2" t="s">
         <v>20</v>
       </c>
@@ -1833,11 +1890,14 @@
       <c r="E15" s="5" t="s">
         <v>278</v>
       </c>
-      <c r="F15" s="7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9" hidden="1">
+      <c r="F15" s="5">
+        <v>1</v>
+      </c>
+      <c r="G15" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10">
       <c r="A16" s="2" t="s">
         <v>21</v>
       </c>
@@ -1853,11 +1913,14 @@
       <c r="E16" s="5" t="s">
         <v>288</v>
       </c>
-      <c r="F16" s="7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" hidden="1">
+      <c r="F16" s="5">
+        <v>0</v>
+      </c>
+      <c r="G16" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8">
       <c r="A17" s="2" t="s">
         <v>22</v>
       </c>
@@ -1873,11 +1936,14 @@
       <c r="E17" s="5" t="s">
         <v>287</v>
       </c>
-      <c r="F17" s="7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" hidden="1">
+      <c r="F17" s="5">
+        <v>1</v>
+      </c>
+      <c r="G17" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8">
       <c r="A18" s="2" t="s">
         <v>23</v>
       </c>
@@ -1893,11 +1959,14 @@
       <c r="E18" s="5" t="s">
         <v>287</v>
       </c>
-      <c r="F18" s="7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7">
+      <c r="F18" s="5">
+        <v>1</v>
+      </c>
+      <c r="G18" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8">
       <c r="A19" s="2" t="s">
         <v>24</v>
       </c>
@@ -1910,11 +1979,14 @@
       <c r="D19" s="2" t="s">
         <v>222</v>
       </c>
-      <c r="F19" s="7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7">
+      <c r="F19" s="5">
+        <v>1</v>
+      </c>
+      <c r="G19" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8">
       <c r="A20" s="2" t="s">
         <v>25</v>
       </c>
@@ -1927,11 +1999,14 @@
       <c r="D20" s="2" t="s">
         <v>223</v>
       </c>
-      <c r="F20" s="7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7">
+      <c r="F20" s="5">
+        <v>1</v>
+      </c>
+      <c r="G20" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8">
       <c r="A21" s="2" t="s">
         <v>26</v>
       </c>
@@ -1944,11 +2019,14 @@
       <c r="D21" s="2" t="s">
         <v>229</v>
       </c>
-      <c r="F21" s="7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7">
+      <c r="F21" s="5">
+        <v>1</v>
+      </c>
+      <c r="G21" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8">
       <c r="A22" s="2" t="s">
         <v>27</v>
       </c>
@@ -1961,11 +2039,14 @@
       <c r="D22" s="2" t="s">
         <v>276</v>
       </c>
-      <c r="F22" s="7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7">
+      <c r="F22" s="5">
+        <v>1</v>
+      </c>
+      <c r="G22" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8">
       <c r="A23" s="2" t="s">
         <v>28</v>
       </c>
@@ -1981,11 +2062,14 @@
       <c r="E23" s="5" t="s">
         <v>289</v>
       </c>
-      <c r="F23" s="7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7" hidden="1">
+      <c r="F23" s="5">
+        <v>1</v>
+      </c>
+      <c r="G23" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8">
       <c r="A24" s="2" t="s">
         <v>29</v>
       </c>
@@ -2001,12 +2085,15 @@
       <c r="E24" s="5" t="s">
         <v>290</v>
       </c>
-      <c r="F24" s="7">
-        <v>0</v>
-      </c>
-      <c r="G24" s="12"/>
-    </row>
-    <row r="25" spans="1:7" hidden="1">
+      <c r="F24" s="5">
+        <v>1</v>
+      </c>
+      <c r="G24" s="7">
+        <v>0</v>
+      </c>
+      <c r="H24" s="12"/>
+    </row>
+    <row r="25" spans="1:8">
       <c r="A25" s="2" t="s">
         <v>30</v>
       </c>
@@ -2022,12 +2109,15 @@
       <c r="E25" s="2" t="s">
         <v>291</v>
       </c>
-      <c r="F25" s="7">
-        <v>0</v>
-      </c>
-      <c r="G25" s="12"/>
-    </row>
-    <row r="26" spans="1:7" hidden="1">
+      <c r="F25" s="2">
+        <v>1</v>
+      </c>
+      <c r="G25" s="7">
+        <v>0</v>
+      </c>
+      <c r="H25" s="12"/>
+    </row>
+    <row r="26" spans="1:8">
       <c r="A26" s="2" t="s">
         <v>31</v>
       </c>
@@ -2043,12 +2133,15 @@
       <c r="E26" s="5" t="s">
         <v>291</v>
       </c>
-      <c r="F26" s="7">
-        <v>0</v>
-      </c>
-      <c r="G26" s="12"/>
-    </row>
-    <row r="27" spans="1:7">
+      <c r="F26" s="5">
+        <v>0</v>
+      </c>
+      <c r="G26" s="7">
+        <v>0</v>
+      </c>
+      <c r="H26" s="12"/>
+    </row>
+    <row r="27" spans="1:8">
       <c r="A27" s="3" t="s">
         <v>32</v>
       </c>
@@ -2064,11 +2157,14 @@
       <c r="E27" s="2" t="s">
         <v>271</v>
       </c>
-      <c r="F27" s="7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7" hidden="1">
+      <c r="F27" s="2">
+        <v>1</v>
+      </c>
+      <c r="G27" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8">
       <c r="A28" s="2" t="s">
         <v>33</v>
       </c>
@@ -2084,11 +2180,14 @@
       <c r="E28" s="2" t="s">
         <v>285</v>
       </c>
-      <c r="F28" s="8">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7" hidden="1">
+      <c r="F28" s="2">
+        <v>1</v>
+      </c>
+      <c r="G28" s="8">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8">
       <c r="A29" s="2" t="s">
         <v>34</v>
       </c>
@@ -2101,11 +2200,14 @@
       <c r="D29" s="2" t="s">
         <v>231</v>
       </c>
-      <c r="F29" s="7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7" hidden="1">
+      <c r="F29" s="5">
+        <v>0</v>
+      </c>
+      <c r="G29" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8">
       <c r="A30" s="2" t="s">
         <v>35</v>
       </c>
@@ -2118,11 +2220,14 @@
       <c r="D30" s="2" t="s">
         <v>232</v>
       </c>
-      <c r="F30" s="7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7" hidden="1">
+      <c r="F30" s="5">
+        <v>0</v>
+      </c>
+      <c r="G30" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8">
       <c r="A31" s="2" t="s">
         <v>36</v>
       </c>
@@ -2135,11 +2240,14 @@
       <c r="D31" s="2" t="s">
         <v>233</v>
       </c>
-      <c r="F31" s="7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7">
+      <c r="F31" s="5">
+        <v>0</v>
+      </c>
+      <c r="G31" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8">
       <c r="A32" s="2" t="s">
         <v>37</v>
       </c>
@@ -2152,11 +2260,14 @@
       <c r="D32" s="2" t="s">
         <v>234</v>
       </c>
-      <c r="F32" s="7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="33" spans="1:7">
+      <c r="F32" s="5">
+        <v>0</v>
+      </c>
+      <c r="G32" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8">
       <c r="A33" s="2" t="s">
         <v>38</v>
       </c>
@@ -2169,11 +2280,14 @@
       <c r="D33" s="2" t="s">
         <v>235</v>
       </c>
-      <c r="F33" s="7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="34" spans="1:7">
+      <c r="F33" s="5">
+        <v>0</v>
+      </c>
+      <c r="G33" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8">
       <c r="A34" s="2" t="s">
         <v>40</v>
       </c>
@@ -2186,11 +2300,14 @@
       <c r="D34" s="2" t="s">
         <v>236</v>
       </c>
-      <c r="F34" s="7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="35" spans="1:7" hidden="1">
+      <c r="F34" s="5">
+        <v>0</v>
+      </c>
+      <c r="G34" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8">
       <c r="A35" s="2" t="s">
         <v>41</v>
       </c>
@@ -2204,11 +2321,14 @@
       <c r="E35" s="5" t="s">
         <v>285</v>
       </c>
-      <c r="F35" s="7">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="36" spans="1:7">
+      <c r="F35" s="5">
+        <v>0</v>
+      </c>
+      <c r="G35" s="7">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8">
       <c r="A36" s="3" t="s">
         <v>42</v>
       </c>
@@ -2224,11 +2344,14 @@
       <c r="E36" s="2" t="s">
         <v>272</v>
       </c>
-      <c r="F36" s="7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="37" spans="1:7">
+      <c r="F36" s="2">
+        <v>1</v>
+      </c>
+      <c r="G36" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8">
       <c r="A37" s="2" t="s">
         <v>43</v>
       </c>
@@ -2244,11 +2367,14 @@
       <c r="E37" s="2" t="s">
         <v>273</v>
       </c>
-      <c r="F37" s="7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="38" spans="1:7">
+      <c r="F37" s="2">
+        <v>0</v>
+      </c>
+      <c r="G37" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8">
       <c r="A38" s="2" t="s">
         <v>44</v>
       </c>
@@ -2259,11 +2385,14 @@
         <v>45</v>
       </c>
       <c r="D38" s="2"/>
-      <c r="F38" s="7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="39" spans="1:7">
+      <c r="F38" s="5">
+        <v>1</v>
+      </c>
+      <c r="G38" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8">
       <c r="A39" s="2" t="s">
         <v>46</v>
       </c>
@@ -2277,11 +2406,14 @@
       <c r="E39" s="5" t="s">
         <v>290</v>
       </c>
-      <c r="F39" s="7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="40" spans="1:7">
+      <c r="F39" s="5">
+        <v>1</v>
+      </c>
+      <c r="G39" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8">
       <c r="A40" s="2" t="s">
         <v>47</v>
       </c>
@@ -2295,11 +2427,14 @@
       <c r="E40" s="5" t="s">
         <v>291</v>
       </c>
-      <c r="F40" s="7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="41" spans="1:7">
+      <c r="F40" s="5">
+        <v>1</v>
+      </c>
+      <c r="G40" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8">
       <c r="A41" s="2" t="s">
         <v>49</v>
       </c>
@@ -2313,11 +2448,14 @@
       <c r="E41" s="5" t="s">
         <v>291</v>
       </c>
-      <c r="F41" s="7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="42" spans="1:7">
+      <c r="F41" s="5">
+        <v>1</v>
+      </c>
+      <c r="G41" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8">
       <c r="A42" s="2" t="s">
         <v>50</v>
       </c>
@@ -2330,11 +2468,14 @@
       <c r="D42" s="2" t="s">
         <v>239</v>
       </c>
-      <c r="F42" s="7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="43" spans="1:7" ht="19.2" hidden="1" customHeight="1">
+      <c r="F42" s="5">
+        <v>0</v>
+      </c>
+      <c r="G42" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8" ht="19.2" customHeight="1">
       <c r="A43" s="2" t="s">
         <v>51</v>
       </c>
@@ -2350,12 +2491,15 @@
       <c r="E43" s="5" t="s">
         <v>277</v>
       </c>
-      <c r="F43" s="7">
-        <v>0</v>
-      </c>
-      <c r="G43" s="4"/>
-    </row>
-    <row r="44" spans="1:7" ht="19.2" hidden="1" customHeight="1">
+      <c r="F43" s="5">
+        <v>0</v>
+      </c>
+      <c r="G43" s="7">
+        <v>0</v>
+      </c>
+      <c r="H43" s="4"/>
+    </row>
+    <row r="44" spans="1:8" ht="19.2" customHeight="1">
       <c r="A44" s="2" t="s">
         <v>52</v>
       </c>
@@ -2371,12 +2515,15 @@
       <c r="E44" s="5" t="s">
         <v>277</v>
       </c>
-      <c r="F44" s="7">
-        <v>0</v>
-      </c>
-      <c r="G44" s="4"/>
-    </row>
-    <row r="45" spans="1:7" ht="19.2" hidden="1" customHeight="1">
+      <c r="F44" s="5">
+        <v>0</v>
+      </c>
+      <c r="G44" s="7">
+        <v>0</v>
+      </c>
+      <c r="H44" s="4"/>
+    </row>
+    <row r="45" spans="1:8" ht="19.2" customHeight="1">
       <c r="A45" s="2" t="s">
         <v>53</v>
       </c>
@@ -2392,12 +2539,15 @@
       <c r="E45" s="5" t="s">
         <v>277</v>
       </c>
-      <c r="F45" s="7">
-        <v>0</v>
-      </c>
-      <c r="G45" s="4"/>
-    </row>
-    <row r="46" spans="1:7" hidden="1">
+      <c r="F45" s="5">
+        <v>0</v>
+      </c>
+      <c r="G45" s="7">
+        <v>0</v>
+      </c>
+      <c r="H45" s="4"/>
+    </row>
+    <row r="46" spans="1:8">
       <c r="A46" s="2" t="s">
         <v>54</v>
       </c>
@@ -2413,12 +2563,15 @@
       <c r="E46" s="5" t="s">
         <v>277</v>
       </c>
-      <c r="F46" s="7">
-        <v>0</v>
-      </c>
-      <c r="G46" s="4"/>
-    </row>
-    <row r="47" spans="1:7" hidden="1">
+      <c r="F46" s="5">
+        <v>0</v>
+      </c>
+      <c r="G46" s="7">
+        <v>0</v>
+      </c>
+      <c r="H46" s="4"/>
+    </row>
+    <row r="47" spans="1:8">
       <c r="A47" s="2" t="s">
         <v>55</v>
       </c>
@@ -2432,12 +2585,15 @@
       <c r="E47" s="5" t="s">
         <v>277</v>
       </c>
-      <c r="F47" s="7">
-        <v>0</v>
-      </c>
-      <c r="G47" s="4"/>
-    </row>
-    <row r="48" spans="1:7" hidden="1">
+      <c r="F47" s="5">
+        <v>0</v>
+      </c>
+      <c r="G47" s="7">
+        <v>0</v>
+      </c>
+      <c r="H47" s="4"/>
+    </row>
+    <row r="48" spans="1:8">
       <c r="A48" s="2" t="s">
         <v>56</v>
       </c>
@@ -2450,11 +2606,14 @@
       <c r="D48" s="2" t="s">
         <v>244</v>
       </c>
-      <c r="F48" s="7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="49" spans="1:6" hidden="1">
+      <c r="F48" s="5">
+        <v>0</v>
+      </c>
+      <c r="G48" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7">
       <c r="A49" s="2" t="s">
         <v>57</v>
       </c>
@@ -2467,11 +2626,14 @@
       <c r="D49" s="2" t="s">
         <v>245</v>
       </c>
-      <c r="F49" s="7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="50" spans="1:6" hidden="1">
+      <c r="F49" s="5">
+        <v>0</v>
+      </c>
+      <c r="G49" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7">
       <c r="A50" s="2" t="s">
         <v>58</v>
       </c>
@@ -2484,11 +2646,14 @@
       <c r="D50" s="2" t="s">
         <v>246</v>
       </c>
-      <c r="F50" s="7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="51" spans="1:6" hidden="1">
+      <c r="F50" s="5">
+        <v>0</v>
+      </c>
+      <c r="G50" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7">
       <c r="A51" s="2" t="s">
         <v>59</v>
       </c>
@@ -2499,11 +2664,14 @@
         <v>39</v>
       </c>
       <c r="D51" s="2"/>
-      <c r="F51" s="7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="52" spans="1:6" hidden="1">
+      <c r="F51" s="5">
+        <v>0</v>
+      </c>
+      <c r="G51" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7">
       <c r="A52" s="2" t="s">
         <v>60</v>
       </c>
@@ -2514,11 +2682,14 @@
         <v>39</v>
       </c>
       <c r="D52" s="2"/>
-      <c r="F52" s="7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="53" spans="1:6" hidden="1">
+      <c r="F52" s="5">
+        <v>0</v>
+      </c>
+      <c r="G52" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7">
       <c r="A53" s="2" t="s">
         <v>61</v>
       </c>
@@ -2529,11 +2700,14 @@
         <v>6</v>
       </c>
       <c r="D53" s="2"/>
-      <c r="F53" s="7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="54" spans="1:6">
+      <c r="F53" s="5">
+        <v>0</v>
+      </c>
+      <c r="G53" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7">
       <c r="A54" s="2" t="s">
         <v>62</v>
       </c>
@@ -2546,11 +2720,14 @@
       <c r="D54" s="2" t="s">
         <v>247</v>
       </c>
-      <c r="F54" s="7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="55" spans="1:6">
+      <c r="F54" s="5">
+        <v>0</v>
+      </c>
+      <c r="G54" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7">
       <c r="A55" s="2" t="s">
         <v>63</v>
       </c>
@@ -2561,11 +2738,14 @@
         <v>39</v>
       </c>
       <c r="D55" s="2"/>
-      <c r="F55" s="7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="56" spans="1:6">
+      <c r="F55" s="5">
+        <v>0</v>
+      </c>
+      <c r="G55" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7">
       <c r="A56" s="2" t="s">
         <v>64</v>
       </c>
@@ -2576,11 +2756,14 @@
         <v>39</v>
       </c>
       <c r="D56" s="2"/>
-      <c r="F56" s="7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="57" spans="1:6">
+      <c r="F56" s="5">
+        <v>0</v>
+      </c>
+      <c r="G56" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7">
       <c r="A57" s="2" t="s">
         <v>65</v>
       </c>
@@ -2591,11 +2774,14 @@
         <v>48</v>
       </c>
       <c r="D57" s="2"/>
-      <c r="F57" s="7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="58" spans="1:6" hidden="1">
+      <c r="F57" s="5">
+        <v>0</v>
+      </c>
+      <c r="G57" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7">
       <c r="A58" s="2" t="s">
         <v>66</v>
       </c>
@@ -2606,11 +2792,14 @@
         <v>39</v>
       </c>
       <c r="D58" s="2"/>
-      <c r="F58" s="7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="59" spans="1:6" hidden="1">
+      <c r="F58" s="5">
+        <v>0</v>
+      </c>
+      <c r="G58" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7">
       <c r="A59" s="2" t="s">
         <v>67</v>
       </c>
@@ -2621,11 +2810,14 @@
         <v>39</v>
       </c>
       <c r="D59" s="2"/>
-      <c r="F59" s="7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="60" spans="1:6" hidden="1">
+      <c r="F59" s="5">
+        <v>0</v>
+      </c>
+      <c r="G59" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7">
       <c r="A60" s="2" t="s">
         <v>68</v>
       </c>
@@ -2636,11 +2828,14 @@
         <v>39</v>
       </c>
       <c r="D60" s="2"/>
-      <c r="F60" s="7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="61" spans="1:6" hidden="1">
+      <c r="F60" s="5">
+        <v>0</v>
+      </c>
+      <c r="G60" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="1:7">
       <c r="A61" s="2" t="s">
         <v>69</v>
       </c>
@@ -2651,11 +2846,14 @@
         <v>39</v>
       </c>
       <c r="D61" s="2"/>
-      <c r="F61" s="7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="62" spans="1:6" hidden="1">
+      <c r="F61" s="5">
+        <v>0</v>
+      </c>
+      <c r="G61" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="1:7">
       <c r="A62" s="2" t="s">
         <v>70</v>
       </c>
@@ -2666,11 +2864,14 @@
         <v>39</v>
       </c>
       <c r="D62" s="2"/>
-      <c r="F62" s="7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="63" spans="1:6" hidden="1">
+      <c r="F62" s="5">
+        <v>0</v>
+      </c>
+      <c r="G62" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="1:7">
       <c r="A63" s="2" t="s">
         <v>71</v>
       </c>
@@ -2681,11 +2882,14 @@
         <v>39</v>
       </c>
       <c r="D63" s="2"/>
-      <c r="F63" s="7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="64" spans="1:6">
+      <c r="F63" s="5">
+        <v>0</v>
+      </c>
+      <c r="G63" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="1:7">
       <c r="A64" s="2" t="s">
         <v>72</v>
       </c>
@@ -2699,11 +2903,14 @@
       <c r="E64" s="5" t="s">
         <v>292</v>
       </c>
-      <c r="F64" s="7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="65" spans="1:7">
+      <c r="F64" s="5">
+        <v>0</v>
+      </c>
+      <c r="G64" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="65" spans="1:8">
       <c r="A65" s="2" t="s">
         <v>73</v>
       </c>
@@ -2714,11 +2921,14 @@
         <v>8</v>
       </c>
       <c r="D65" s="2"/>
-      <c r="F65" s="7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="66" spans="1:7">
+      <c r="F65" s="5">
+        <v>0</v>
+      </c>
+      <c r="G65" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="66" spans="1:8">
       <c r="A66" s="3" t="s">
         <v>74</v>
       </c>
@@ -2734,11 +2944,14 @@
       <c r="E66" s="5" t="s">
         <v>293</v>
       </c>
-      <c r="F66" s="7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="67" spans="1:7" hidden="1">
+      <c r="F66" s="5">
+        <v>1</v>
+      </c>
+      <c r="G66" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="67" spans="1:8">
       <c r="A67" s="2" t="s">
         <v>75</v>
       </c>
@@ -2752,11 +2965,14 @@
       <c r="E67" s="5" t="s">
         <v>285</v>
       </c>
-      <c r="F67" s="7">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="68" spans="1:7">
+      <c r="F67" s="5">
+        <v>0</v>
+      </c>
+      <c r="G67" s="7">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="68" spans="1:8">
       <c r="A68" s="2" t="s">
         <v>76</v>
       </c>
@@ -2772,12 +2988,15 @@
       <c r="E68" s="5" t="s">
         <v>278</v>
       </c>
-      <c r="F68" s="7">
-        <v>1</v>
-      </c>
-      <c r="G68" s="12"/>
-    </row>
-    <row r="69" spans="1:7">
+      <c r="F68" s="5">
+        <v>1</v>
+      </c>
+      <c r="G68" s="7">
+        <v>1</v>
+      </c>
+      <c r="H68" s="12"/>
+    </row>
+    <row r="69" spans="1:8">
       <c r="A69" s="2" t="s">
         <v>77</v>
       </c>
@@ -2791,12 +3010,15 @@
       <c r="E69" s="5" t="s">
         <v>278</v>
       </c>
-      <c r="F69" s="7">
-        <v>1</v>
-      </c>
-      <c r="G69" s="12"/>
-    </row>
-    <row r="70" spans="1:7" hidden="1">
+      <c r="F69" s="5">
+        <v>1</v>
+      </c>
+      <c r="G69" s="7">
+        <v>1</v>
+      </c>
+      <c r="H69" s="12"/>
+    </row>
+    <row r="70" spans="1:8">
       <c r="A70" s="2" t="s">
         <v>78</v>
       </c>
@@ -2810,11 +3032,14 @@
       <c r="E70" s="5" t="s">
         <v>294</v>
       </c>
-      <c r="F70" s="7">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="71" spans="1:7" hidden="1">
+      <c r="F70" s="5">
+        <v>0</v>
+      </c>
+      <c r="G70" s="7">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="71" spans="1:8">
       <c r="A71" s="2" t="s">
         <v>79</v>
       </c>
@@ -2828,11 +3053,14 @@
       <c r="E71" s="5" t="s">
         <v>294</v>
       </c>
-      <c r="F71" s="7">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="72" spans="1:7" hidden="1">
+      <c r="F71" s="5">
+        <v>0</v>
+      </c>
+      <c r="G71" s="7">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="72" spans="1:8">
       <c r="A72" s="2" t="s">
         <v>80</v>
       </c>
@@ -2846,11 +3074,14 @@
       <c r="E72" s="5" t="s">
         <v>294</v>
       </c>
-      <c r="F72" s="7">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="73" spans="1:7" hidden="1">
+      <c r="F72" s="5">
+        <v>0</v>
+      </c>
+      <c r="G72" s="7">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="73" spans="1:8">
       <c r="A73" s="2" t="s">
         <v>81</v>
       </c>
@@ -2864,11 +3095,14 @@
       <c r="E73" s="5" t="s">
         <v>294</v>
       </c>
-      <c r="F73" s="7">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="74" spans="1:7" hidden="1">
+      <c r="F73" s="5">
+        <v>0</v>
+      </c>
+      <c r="G73" s="7">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="74" spans="1:8">
       <c r="A74" s="2" t="s">
         <v>82</v>
       </c>
@@ -2882,11 +3116,14 @@
       <c r="E74" s="5" t="s">
         <v>294</v>
       </c>
-      <c r="F74" s="7">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="75" spans="1:7" hidden="1">
+      <c r="F74" s="5">
+        <v>0</v>
+      </c>
+      <c r="G74" s="7">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="75" spans="1:8">
       <c r="A75" s="2" t="s">
         <v>83</v>
       </c>
@@ -2900,11 +3137,14 @@
       <c r="E75" s="5" t="s">
         <v>294</v>
       </c>
-      <c r="F75" s="7">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="76" spans="1:7" hidden="1">
+      <c r="F75" s="5">
+        <v>0</v>
+      </c>
+      <c r="G75" s="7">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="76" spans="1:8">
       <c r="A76" s="2" t="s">
         <v>84</v>
       </c>
@@ -2918,11 +3158,14 @@
       <c r="E76" s="5" t="s">
         <v>294</v>
       </c>
-      <c r="F76" s="7">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="77" spans="1:7" hidden="1">
+      <c r="F76" s="5">
+        <v>0</v>
+      </c>
+      <c r="G76" s="7">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="77" spans="1:8">
       <c r="A77" s="2" t="s">
         <v>85</v>
       </c>
@@ -2936,11 +3179,14 @@
       <c r="E77" s="5" t="s">
         <v>294</v>
       </c>
-      <c r="F77" s="7">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="78" spans="1:7" hidden="1">
+      <c r="F77" s="5">
+        <v>0</v>
+      </c>
+      <c r="G77" s="7">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="78" spans="1:8">
       <c r="A78" s="2" t="s">
         <v>86</v>
       </c>
@@ -2954,11 +3200,14 @@
       <c r="E78" s="5" t="s">
         <v>294</v>
       </c>
-      <c r="F78" s="7">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="79" spans="1:7" hidden="1">
+      <c r="F78" s="5">
+        <v>0</v>
+      </c>
+      <c r="G78" s="7">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="79" spans="1:8">
       <c r="A79" s="2" t="s">
         <v>87</v>
       </c>
@@ -2969,11 +3218,14 @@
         <v>6</v>
       </c>
       <c r="D79" s="2"/>
-      <c r="F79" s="7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="80" spans="1:7">
+      <c r="F79" s="5">
+        <v>0</v>
+      </c>
+      <c r="G79" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80" spans="1:8">
       <c r="A80" s="2" t="s">
         <v>88</v>
       </c>
@@ -2986,11 +3238,14 @@
       <c r="D80" s="2" t="s">
         <v>256</v>
       </c>
-      <c r="F80" s="7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="81" spans="1:6">
+      <c r="F80" s="5">
+        <v>0</v>
+      </c>
+      <c r="G80" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="81" spans="1:7">
       <c r="A81" s="2" t="s">
         <v>89</v>
       </c>
@@ -3003,11 +3258,14 @@
       <c r="D81" s="2" t="s">
         <v>257</v>
       </c>
-      <c r="F81" s="7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="82" spans="1:6">
+      <c r="F81" s="5">
+        <v>0</v>
+      </c>
+      <c r="G81" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="82" spans="1:7">
       <c r="A82" s="2" t="s">
         <v>90</v>
       </c>
@@ -3020,11 +3278,14 @@
       <c r="D82" s="2" t="s">
         <v>258</v>
       </c>
-      <c r="F82" s="7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="83" spans="1:6">
+      <c r="F82" s="5">
+        <v>0</v>
+      </c>
+      <c r="G82" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="83" spans="1:7">
       <c r="A83" s="2" t="s">
         <v>91</v>
       </c>
@@ -3037,11 +3298,14 @@
       <c r="D83" s="2" t="s">
         <v>259</v>
       </c>
-      <c r="F83" s="7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="84" spans="1:6" hidden="1">
+      <c r="F83" s="5">
+        <v>0</v>
+      </c>
+      <c r="G83" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="84" spans="1:7">
       <c r="A84" s="2" t="s">
         <v>92</v>
       </c>
@@ -3052,11 +3316,14 @@
         <v>6</v>
       </c>
       <c r="D84" s="2"/>
-      <c r="F84" s="7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="85" spans="1:6" hidden="1">
+      <c r="F84" s="5">
+        <v>0</v>
+      </c>
+      <c r="G84" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="1:7">
       <c r="A85" s="2" t="s">
         <v>93</v>
       </c>
@@ -3067,11 +3334,14 @@
         <v>8</v>
       </c>
       <c r="D85" s="2"/>
-      <c r="F85" s="7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="86" spans="1:6" hidden="1">
+      <c r="F85" s="5">
+        <v>0</v>
+      </c>
+      <c r="G85" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="1:7">
       <c r="A86" s="2" t="s">
         <v>94</v>
       </c>
@@ -3082,11 +3352,14 @@
         <v>8</v>
       </c>
       <c r="D86" s="2"/>
-      <c r="F86" s="7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="87" spans="1:6" hidden="1">
+      <c r="F86" s="5">
+        <v>0</v>
+      </c>
+      <c r="G86" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="1:7">
       <c r="A87" s="2" t="s">
         <v>95</v>
       </c>
@@ -3097,11 +3370,14 @@
         <v>8</v>
       </c>
       <c r="D87" s="2"/>
-      <c r="F87" s="7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="88" spans="1:6" hidden="1">
+      <c r="F87" s="5">
+        <v>0</v>
+      </c>
+      <c r="G87" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="1:7">
       <c r="A88" s="2" t="s">
         <v>96</v>
       </c>
@@ -3112,11 +3388,14 @@
         <v>6</v>
       </c>
       <c r="D88" s="2"/>
-      <c r="F88" s="7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="89" spans="1:6" hidden="1">
+      <c r="F88" s="5">
+        <v>0</v>
+      </c>
+      <c r="G88" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="1:7">
       <c r="A89" s="2" t="s">
         <v>97</v>
       </c>
@@ -3127,11 +3406,14 @@
         <v>6</v>
       </c>
       <c r="D89" s="2"/>
-      <c r="F89" s="7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="90" spans="1:6">
+      <c r="F89" s="5">
+        <v>0</v>
+      </c>
+      <c r="G89" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="1:7">
       <c r="A90" s="2" t="s">
         <v>98</v>
       </c>
@@ -3142,11 +3424,14 @@
         <v>8</v>
       </c>
       <c r="D90" s="2"/>
-      <c r="F90" s="7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="91" spans="1:6" hidden="1">
+      <c r="F90" s="5">
+        <v>0</v>
+      </c>
+      <c r="G90" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="91" spans="1:7">
       <c r="A91" s="2" t="s">
         <v>99</v>
       </c>
@@ -3160,11 +3445,14 @@
       <c r="E91" s="5" t="s">
         <v>285</v>
       </c>
-      <c r="F91" s="7">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="92" spans="1:6" hidden="1">
+      <c r="F91" s="5">
+        <v>0</v>
+      </c>
+      <c r="G91" s="7">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="92" spans="1:7">
       <c r="A92" s="2" t="s">
         <v>100</v>
       </c>
@@ -3175,11 +3463,14 @@
         <v>6</v>
       </c>
       <c r="D92" s="2"/>
-      <c r="F92" s="7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="93" spans="1:6" hidden="1">
+      <c r="F92" s="5">
+        <v>1</v>
+      </c>
+      <c r="G92" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="1:7">
       <c r="A93" s="2" t="s">
         <v>101</v>
       </c>
@@ -3193,11 +3484,14 @@
       <c r="E93" s="5" t="s">
         <v>285</v>
       </c>
-      <c r="F93" s="7">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="94" spans="1:6" hidden="1">
+      <c r="F93" s="5">
+        <v>0</v>
+      </c>
+      <c r="G93" s="7">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="94" spans="1:7">
       <c r="A94" s="2" t="s">
         <v>102</v>
       </c>
@@ -3211,11 +3505,14 @@
       <c r="E94" s="5" t="s">
         <v>285</v>
       </c>
-      <c r="F94" s="7">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="95" spans="1:6" hidden="1">
+      <c r="F94" s="5">
+        <v>0</v>
+      </c>
+      <c r="G94" s="7">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="95" spans="1:7">
       <c r="A95" s="2" t="s">
         <v>103</v>
       </c>
@@ -3229,11 +3526,14 @@
       <c r="E95" s="5" t="s">
         <v>285</v>
       </c>
-      <c r="F95" s="7">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="96" spans="1:6" hidden="1">
+      <c r="F95" s="5">
+        <v>0</v>
+      </c>
+      <c r="G95" s="7">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="96" spans="1:7">
       <c r="A96" s="2" t="s">
         <v>104</v>
       </c>
@@ -3247,11 +3547,14 @@
       <c r="E96" s="5" t="s">
         <v>295</v>
       </c>
-      <c r="F96" s="7">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="97" spans="1:6" hidden="1">
+      <c r="F96" s="5">
+        <v>0</v>
+      </c>
+      <c r="G96" s="7">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="97" spans="1:7">
       <c r="A97" s="2" t="s">
         <v>105</v>
       </c>
@@ -3265,11 +3568,14 @@
       <c r="E97" s="5" t="s">
         <v>285</v>
       </c>
-      <c r="F97" s="7">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="98" spans="1:6" hidden="1">
+      <c r="F97" s="5">
+        <v>0</v>
+      </c>
+      <c r="G97" s="7">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="98" spans="1:7">
       <c r="A98" s="2" t="s">
         <v>106</v>
       </c>
@@ -3280,11 +3586,14 @@
         <v>6</v>
       </c>
       <c r="D98" s="2"/>
-      <c r="F98" s="7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="99" spans="1:6" hidden="1">
+      <c r="F98" s="5">
+        <v>0</v>
+      </c>
+      <c r="G98" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="1:7">
       <c r="A99" s="2" t="s">
         <v>107</v>
       </c>
@@ -3298,11 +3607,14 @@
       <c r="E99" s="5" t="s">
         <v>285</v>
       </c>
-      <c r="F99" s="7">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="100" spans="1:6" hidden="1">
+      <c r="F99" s="5">
+        <v>0</v>
+      </c>
+      <c r="G99" s="7">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="100" spans="1:7">
       <c r="A100" s="2" t="s">
         <v>108</v>
       </c>
@@ -3313,11 +3625,14 @@
         <v>6</v>
       </c>
       <c r="D100" s="2"/>
-      <c r="F100" s="7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101" spans="1:6" hidden="1">
+      <c r="F100" s="5">
+        <v>0</v>
+      </c>
+      <c r="G100" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="1:7">
       <c r="A101" s="2" t="s">
         <v>109</v>
       </c>
@@ -3328,11 +3643,14 @@
         <v>6</v>
       </c>
       <c r="D101" s="2"/>
-      <c r="F101" s="7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="102" spans="1:6" hidden="1">
+      <c r="F101" s="5">
+        <v>0</v>
+      </c>
+      <c r="G101" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="1:7">
       <c r="A102" s="2" t="s">
         <v>110</v>
       </c>
@@ -3343,11 +3661,14 @@
         <v>6</v>
       </c>
       <c r="D102" s="2"/>
-      <c r="F102" s="7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="103" spans="1:6" hidden="1">
+      <c r="F102" s="5">
+        <v>0</v>
+      </c>
+      <c r="G102" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="103" spans="1:7">
       <c r="A103" s="2" t="s">
         <v>111</v>
       </c>
@@ -3358,11 +3679,14 @@
         <v>6</v>
       </c>
       <c r="D103" s="2"/>
-      <c r="F103" s="7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="104" spans="1:6">
+      <c r="F103" s="5">
+        <v>0</v>
+      </c>
+      <c r="G103" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="104" spans="1:7">
       <c r="A104" s="2" t="s">
         <v>112</v>
       </c>
@@ -3376,11 +3700,14 @@
       <c r="E104" s="5" t="s">
         <v>293</v>
       </c>
-      <c r="F104" s="7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="105" spans="1:6" hidden="1">
+      <c r="F104" s="5">
+        <v>1</v>
+      </c>
+      <c r="G104" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="105" spans="1:7">
       <c r="A105" s="2" t="s">
         <v>113</v>
       </c>
@@ -3391,11 +3718,14 @@
         <v>6</v>
       </c>
       <c r="D105" s="2"/>
-      <c r="F105" s="7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="106" spans="1:6" hidden="1">
+      <c r="F105" s="5">
+        <v>0</v>
+      </c>
+      <c r="G105" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="106" spans="1:7">
       <c r="A106" s="2" t="s">
         <v>114</v>
       </c>
@@ -3409,11 +3739,14 @@
       <c r="E106" s="5" t="s">
         <v>296</v>
       </c>
-      <c r="F106" s="7">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="107" spans="1:6" hidden="1">
+      <c r="F106" s="5">
+        <v>0</v>
+      </c>
+      <c r="G106" s="7">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="107" spans="1:7">
       <c r="A107" s="2" t="s">
         <v>115</v>
       </c>
@@ -3427,11 +3760,14 @@
       <c r="E107" s="5" t="s">
         <v>296</v>
       </c>
-      <c r="F107" s="7">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="108" spans="1:6" hidden="1">
+      <c r="F107" s="5">
+        <v>0</v>
+      </c>
+      <c r="G107" s="7">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="108" spans="1:7">
       <c r="A108" s="2" t="s">
         <v>116</v>
       </c>
@@ -3445,11 +3781,14 @@
       <c r="E108" s="5" t="s">
         <v>296</v>
       </c>
-      <c r="F108" s="7">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="109" spans="1:6" hidden="1">
+      <c r="F108" s="5">
+        <v>0</v>
+      </c>
+      <c r="G108" s="7">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="109" spans="1:7">
       <c r="A109" s="2" t="s">
         <v>117</v>
       </c>
@@ -3463,11 +3802,14 @@
       <c r="E109" s="5" t="s">
         <v>296</v>
       </c>
-      <c r="F109" s="7">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="110" spans="1:6" hidden="1">
+      <c r="F109" s="5">
+        <v>0</v>
+      </c>
+      <c r="G109" s="7">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="110" spans="1:7">
       <c r="A110" s="2" t="s">
         <v>118</v>
       </c>
@@ -3481,11 +3823,14 @@
       <c r="E110" s="5" t="s">
         <v>296</v>
       </c>
-      <c r="F110" s="7">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="111" spans="1:6" hidden="1">
+      <c r="F110" s="5">
+        <v>0</v>
+      </c>
+      <c r="G110" s="7">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="111" spans="1:7">
       <c r="A111" s="2" t="s">
         <v>119</v>
       </c>
@@ -3499,11 +3844,14 @@
       <c r="E111" s="5" t="s">
         <v>296</v>
       </c>
-      <c r="F111" s="7">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="112" spans="1:6" hidden="1">
+      <c r="F111" s="5">
+        <v>0</v>
+      </c>
+      <c r="G111" s="7">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="112" spans="1:7">
       <c r="A112" s="2" t="s">
         <v>120</v>
       </c>
@@ -3517,11 +3865,14 @@
       <c r="E112" s="5" t="s">
         <v>296</v>
       </c>
-      <c r="F112" s="7">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="113" spans="1:6" hidden="1">
+      <c r="F112" s="5">
+        <v>0</v>
+      </c>
+      <c r="G112" s="7">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="113" spans="1:7">
       <c r="A113" s="2" t="s">
         <v>121</v>
       </c>
@@ -3535,11 +3886,14 @@
       <c r="E113" s="5" t="s">
         <v>296</v>
       </c>
-      <c r="F113" s="7">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="114" spans="1:6" hidden="1">
+      <c r="F113" s="5">
+        <v>0</v>
+      </c>
+      <c r="G113" s="7">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="114" spans="1:7">
       <c r="A114" s="2" t="s">
         <v>122</v>
       </c>
@@ -3553,11 +3907,14 @@
       <c r="E114" s="5" t="s">
         <v>296</v>
       </c>
-      <c r="F114" s="7">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="115" spans="1:6" hidden="1">
+      <c r="F114" s="5">
+        <v>0</v>
+      </c>
+      <c r="G114" s="7">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="115" spans="1:7">
       <c r="A115" s="2" t="s">
         <v>124</v>
       </c>
@@ -3571,11 +3928,14 @@
       <c r="E115" s="5" t="s">
         <v>296</v>
       </c>
-      <c r="F115" s="7">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="116" spans="1:6" hidden="1">
+      <c r="F115" s="5">
+        <v>0</v>
+      </c>
+      <c r="G115" s="7">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="116" spans="1:7">
       <c r="A116" s="2" t="s">
         <v>125</v>
       </c>
@@ -3589,11 +3949,14 @@
       <c r="E116" s="5" t="s">
         <v>296</v>
       </c>
-      <c r="F116" s="7">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="117" spans="1:6" hidden="1">
+      <c r="F116" s="5">
+        <v>0</v>
+      </c>
+      <c r="G116" s="7">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="117" spans="1:7">
       <c r="A117" s="2" t="s">
         <v>126</v>
       </c>
@@ -3607,11 +3970,14 @@
       <c r="E117" s="5" t="s">
         <v>296</v>
       </c>
-      <c r="F117" s="7">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="118" spans="1:6" hidden="1">
+      <c r="F117" s="5">
+        <v>0</v>
+      </c>
+      <c r="G117" s="7">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="118" spans="1:7">
       <c r="A118" s="2" t="s">
         <v>127</v>
       </c>
@@ -3625,11 +3991,14 @@
       <c r="E118" s="5" t="s">
         <v>296</v>
       </c>
-      <c r="F118" s="7">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="119" spans="1:6" hidden="1">
+      <c r="F118" s="5">
+        <v>0</v>
+      </c>
+      <c r="G118" s="7">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="119" spans="1:7">
       <c r="A119" s="2" t="s">
         <v>128</v>
       </c>
@@ -3643,11 +4012,14 @@
       <c r="E119" s="5" t="s">
         <v>296</v>
       </c>
-      <c r="F119" s="7">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="120" spans="1:6" hidden="1">
+      <c r="F119" s="5">
+        <v>0</v>
+      </c>
+      <c r="G119" s="7">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="120" spans="1:7">
       <c r="A120" s="2" t="s">
         <v>129</v>
       </c>
@@ -3661,11 +4033,14 @@
       <c r="E120" s="5" t="s">
         <v>296</v>
       </c>
-      <c r="F120" s="7">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="121" spans="1:6">
+      <c r="F120" s="5">
+        <v>0</v>
+      </c>
+      <c r="G120" s="7">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="121" spans="1:7">
       <c r="A121" s="3" t="s">
         <v>130</v>
       </c>
@@ -3678,11 +4053,14 @@
       <c r="D121" s="2" t="s">
         <v>250</v>
       </c>
-      <c r="F121" s="7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="122" spans="1:6">
+      <c r="F121" s="5">
+        <v>1</v>
+      </c>
+      <c r="G121" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="122" spans="1:7">
       <c r="A122" s="3" t="s">
         <v>131</v>
       </c>
@@ -3695,11 +4073,14 @@
       <c r="D122" s="2" t="s">
         <v>251</v>
       </c>
-      <c r="F122" s="7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="123" spans="1:6">
+      <c r="F122" s="5">
+        <v>0</v>
+      </c>
+      <c r="G122" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="123" spans="1:7">
       <c r="A123" s="3" t="s">
         <v>132</v>
       </c>
@@ -3710,11 +4091,14 @@
         <v>8</v>
       </c>
       <c r="D123" s="2"/>
-      <c r="F123" s="7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="124" spans="1:6">
+      <c r="F123" s="5">
+        <v>0</v>
+      </c>
+      <c r="G123" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="124" spans="1:7">
       <c r="A124" s="3" t="s">
         <v>133</v>
       </c>
@@ -3727,11 +4111,14 @@
       <c r="D124" s="2" t="s">
         <v>252</v>
       </c>
-      <c r="F124" s="7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="125" spans="1:6">
+      <c r="F124" s="5">
+        <v>0</v>
+      </c>
+      <c r="G124" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="125" spans="1:7">
       <c r="A125" s="3" t="s">
         <v>134</v>
       </c>
@@ -3744,11 +4131,14 @@
       <c r="D125" s="2" t="s">
         <v>253</v>
       </c>
-      <c r="F125" s="7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="126" spans="1:6">
+      <c r="F125" s="5">
+        <v>0</v>
+      </c>
+      <c r="G125" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="126" spans="1:7">
       <c r="A126" s="3" t="s">
         <v>135</v>
       </c>
@@ -3764,11 +4154,14 @@
       <c r="E126" s="11" t="s">
         <v>297</v>
       </c>
-      <c r="F126" s="7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="127" spans="1:6">
+      <c r="F126" s="5">
+        <v>1</v>
+      </c>
+      <c r="G126" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="127" spans="1:7">
       <c r="A127" s="3" t="s">
         <v>136</v>
       </c>
@@ -3781,11 +4174,14 @@
       <c r="D127" s="2" t="s">
         <v>255</v>
       </c>
-      <c r="F127" s="7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="128" spans="1:6" hidden="1">
+      <c r="F127" s="5">
+        <v>0</v>
+      </c>
+      <c r="G127" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="128" spans="1:7">
       <c r="A128" s="2" t="s">
         <v>137</v>
       </c>
@@ -3799,11 +4195,14 @@
       <c r="E128" s="5" t="s">
         <v>296</v>
       </c>
-      <c r="F128" s="7">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="129" spans="1:6" hidden="1">
+      <c r="F128" s="5">
+        <v>0</v>
+      </c>
+      <c r="G128" s="7">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="129" spans="1:7">
       <c r="A129" s="2" t="s">
         <v>138</v>
       </c>
@@ -3817,11 +4216,14 @@
       <c r="E129" s="5" t="s">
         <v>296</v>
       </c>
-      <c r="F129" s="7">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="130" spans="1:6" ht="19.2" hidden="1">
+      <c r="F129" s="5">
+        <v>0</v>
+      </c>
+      <c r="G129" s="7">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="130" spans="1:7" ht="19.2">
       <c r="A130" s="2" t="s">
         <v>140</v>
       </c>
@@ -3835,11 +4237,14 @@
       <c r="E130" s="5" t="s">
         <v>296</v>
       </c>
-      <c r="F130" s="7">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="131" spans="1:6" hidden="1">
+      <c r="F130" s="5">
+        <v>0</v>
+      </c>
+      <c r="G130" s="7">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="131" spans="1:7">
       <c r="A131" s="2" t="s">
         <v>141</v>
       </c>
@@ -3853,11 +4258,14 @@
       <c r="E131" s="5" t="s">
         <v>296</v>
       </c>
-      <c r="F131" s="7">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="132" spans="1:6" hidden="1">
+      <c r="F131" s="5">
+        <v>0</v>
+      </c>
+      <c r="G131" s="7">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="132" spans="1:7">
       <c r="A132" s="2" t="s">
         <v>142</v>
       </c>
@@ -3871,11 +4279,14 @@
       <c r="E132" s="5" t="s">
         <v>296</v>
       </c>
-      <c r="F132" s="7">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="133" spans="1:6" hidden="1">
+      <c r="F132" s="5">
+        <v>0</v>
+      </c>
+      <c r="G132" s="7">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="133" spans="1:7">
       <c r="A133" s="2" t="s">
         <v>143</v>
       </c>
@@ -3889,11 +4300,14 @@
       <c r="E133" s="5" t="s">
         <v>296</v>
       </c>
-      <c r="F133" s="7">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="134" spans="1:6" hidden="1">
+      <c r="F133" s="5">
+        <v>0</v>
+      </c>
+      <c r="G133" s="7">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="134" spans="1:7">
       <c r="A134" s="2" t="s">
         <v>144</v>
       </c>
@@ -3907,11 +4321,14 @@
       <c r="E134" s="5" t="s">
         <v>296</v>
       </c>
-      <c r="F134" s="7">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="135" spans="1:6" hidden="1">
+      <c r="F134" s="5">
+        <v>0</v>
+      </c>
+      <c r="G134" s="7">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="135" spans="1:7">
       <c r="A135" s="2" t="s">
         <v>145</v>
       </c>
@@ -3925,11 +4342,14 @@
       <c r="E135" s="5" t="s">
         <v>296</v>
       </c>
-      <c r="F135" s="7">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="136" spans="1:6" hidden="1">
+      <c r="F135" s="5">
+        <v>0</v>
+      </c>
+      <c r="G135" s="7">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="136" spans="1:7">
       <c r="A136" s="2" t="s">
         <v>146</v>
       </c>
@@ -3943,11 +4363,14 @@
       <c r="E136" s="5" t="s">
         <v>296</v>
       </c>
-      <c r="F136" s="7">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="137" spans="1:6" hidden="1">
+      <c r="F136" s="5">
+        <v>0</v>
+      </c>
+      <c r="G136" s="7">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="137" spans="1:7">
       <c r="A137" s="2" t="s">
         <v>147</v>
       </c>
@@ -3961,11 +4384,14 @@
       <c r="E137" s="5" t="s">
         <v>296</v>
       </c>
-      <c r="F137" s="7">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="138" spans="1:6" hidden="1">
+      <c r="F137" s="5">
+        <v>0</v>
+      </c>
+      <c r="G137" s="7">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="138" spans="1:7">
       <c r="A138" s="2" t="s">
         <v>148</v>
       </c>
@@ -3979,11 +4405,14 @@
       <c r="E138" s="5" t="s">
         <v>296</v>
       </c>
-      <c r="F138" s="7">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="139" spans="1:6" hidden="1">
+      <c r="F138" s="5">
+        <v>0</v>
+      </c>
+      <c r="G138" s="7">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="139" spans="1:7">
       <c r="A139" s="2" t="s">
         <v>149</v>
       </c>
@@ -3997,11 +4426,14 @@
       <c r="E139" s="5" t="s">
         <v>296</v>
       </c>
-      <c r="F139" s="7">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="140" spans="1:6" hidden="1">
+      <c r="F139" s="5">
+        <v>0</v>
+      </c>
+      <c r="G139" s="7">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="140" spans="1:7">
       <c r="A140" s="2" t="s">
         <v>150</v>
       </c>
@@ -4015,11 +4447,14 @@
       <c r="E140" s="5" t="s">
         <v>296</v>
       </c>
-      <c r="F140" s="7">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="141" spans="1:6" hidden="1">
+      <c r="F140" s="5">
+        <v>0</v>
+      </c>
+      <c r="G140" s="7">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="141" spans="1:7">
       <c r="A141" s="2" t="s">
         <v>151</v>
       </c>
@@ -4033,11 +4468,14 @@
       <c r="E141" s="5" t="s">
         <v>296</v>
       </c>
-      <c r="F141" s="7">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="142" spans="1:6" hidden="1">
+      <c r="F141" s="5">
+        <v>0</v>
+      </c>
+      <c r="G141" s="7">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="142" spans="1:7">
       <c r="A142" s="2" t="s">
         <v>152</v>
       </c>
@@ -4048,11 +4486,14 @@
         <v>6</v>
       </c>
       <c r="D142" s="2"/>
-      <c r="F142" s="7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="143" spans="1:6" hidden="1">
+      <c r="F142" s="5">
+        <v>0</v>
+      </c>
+      <c r="G142" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="143" spans="1:7">
       <c r="A143" s="2" t="s">
         <v>153</v>
       </c>
@@ -4066,11 +4507,14 @@
       <c r="E143" s="5" t="s">
         <v>285</v>
       </c>
-      <c r="F143" s="7">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="144" spans="1:6" hidden="1">
+      <c r="F143" s="5">
+        <v>0</v>
+      </c>
+      <c r="G143" s="7">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="144" spans="1:7">
       <c r="A144" s="2" t="s">
         <v>154</v>
       </c>
@@ -4081,11 +4525,14 @@
         <v>6</v>
       </c>
       <c r="D144" s="2"/>
-      <c r="F144" s="7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="145" spans="1:6" hidden="1">
+      <c r="F144" s="5">
+        <v>0</v>
+      </c>
+      <c r="G144" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="145" spans="1:7">
       <c r="A145" s="2" t="s">
         <v>155</v>
       </c>
@@ -4096,11 +4543,14 @@
         <v>6</v>
       </c>
       <c r="D145" s="2"/>
-      <c r="F145" s="7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="146" spans="1:6" hidden="1">
+      <c r="F145" s="5">
+        <v>0</v>
+      </c>
+      <c r="G145" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="146" spans="1:7">
       <c r="A146" s="2" t="s">
         <v>156</v>
       </c>
@@ -4111,11 +4561,14 @@
         <v>6</v>
       </c>
       <c r="D146" s="2"/>
-      <c r="F146" s="7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="147" spans="1:6" hidden="1">
+      <c r="F146" s="5">
+        <v>0</v>
+      </c>
+      <c r="G146" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="147" spans="1:7">
       <c r="A147" s="2" t="s">
         <v>157</v>
       </c>
@@ -4126,11 +4579,14 @@
         <v>8</v>
       </c>
       <c r="D147" s="2"/>
-      <c r="F147" s="7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="148" spans="1:6" hidden="1">
+      <c r="F147" s="5">
+        <v>0</v>
+      </c>
+      <c r="G147" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="148" spans="1:7">
       <c r="A148" s="2" t="s">
         <v>158</v>
       </c>
@@ -4141,11 +4597,14 @@
         <v>6</v>
       </c>
       <c r="D148" s="2"/>
-      <c r="F148" s="7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="149" spans="1:6" ht="19.2" hidden="1">
+      <c r="F148" s="5">
+        <v>0</v>
+      </c>
+      <c r="G148" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="149" spans="1:7" ht="19.2">
       <c r="A149" s="2" t="s">
         <v>159</v>
       </c>
@@ -4156,11 +4615,14 @@
         <v>39</v>
       </c>
       <c r="D149" s="2"/>
-      <c r="F149" s="7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="150" spans="1:6" ht="19.2" hidden="1">
+      <c r="F149" s="5">
+        <v>0</v>
+      </c>
+      <c r="G149" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="150" spans="1:7" ht="19.2">
       <c r="A150" s="2" t="s">
         <v>160</v>
       </c>
@@ -4171,11 +4633,14 @@
         <v>39</v>
       </c>
       <c r="D150" s="2"/>
-      <c r="F150" s="7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="151" spans="1:6" ht="19.2" hidden="1">
+      <c r="F150" s="5">
+        <v>0</v>
+      </c>
+      <c r="G150" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="151" spans="1:7" ht="19.2">
       <c r="A151" s="2" t="s">
         <v>161</v>
       </c>
@@ -4186,11 +4651,14 @@
         <v>45</v>
       </c>
       <c r="D151" s="2"/>
-      <c r="F151" s="7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="152" spans="1:6" ht="19.2" hidden="1">
+      <c r="F151" s="5">
+        <v>0</v>
+      </c>
+      <c r="G151" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="152" spans="1:7" ht="19.2">
       <c r="A152" s="2" t="s">
         <v>162</v>
       </c>
@@ -4201,11 +4669,14 @@
         <v>45</v>
       </c>
       <c r="D152" s="2"/>
-      <c r="F152" s="7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="153" spans="1:6" hidden="1">
+      <c r="F152" s="5">
+        <v>0</v>
+      </c>
+      <c r="G152" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="153" spans="1:7">
       <c r="A153" s="2" t="s">
         <v>163</v>
       </c>
@@ -4216,11 +4687,14 @@
         <v>48</v>
       </c>
       <c r="D153" s="2"/>
-      <c r="F153" s="7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="154" spans="1:6" hidden="1">
+      <c r="F153" s="5">
+        <v>0</v>
+      </c>
+      <c r="G153" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="154" spans="1:7">
       <c r="A154" s="2" t="s">
         <v>164</v>
       </c>
@@ -4231,11 +4705,14 @@
         <v>45</v>
       </c>
       <c r="D154" s="2"/>
-      <c r="F154" s="7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="155" spans="1:6" hidden="1">
+      <c r="F154" s="5">
+        <v>0</v>
+      </c>
+      <c r="G154" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="155" spans="1:7">
       <c r="A155" s="2" t="s">
         <v>165</v>
       </c>
@@ -4246,11 +4723,14 @@
         <v>48</v>
       </c>
       <c r="D155" s="2"/>
-      <c r="F155" s="7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="156" spans="1:6" hidden="1">
+      <c r="F155" s="5">
+        <v>0</v>
+      </c>
+      <c r="G155" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="156" spans="1:7">
       <c r="A156" s="2" t="s">
         <v>166</v>
       </c>
@@ -4261,11 +4741,14 @@
         <v>45</v>
       </c>
       <c r="D156" s="2"/>
-      <c r="F156" s="7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="157" spans="1:6" hidden="1">
+      <c r="F156" s="5">
+        <v>0</v>
+      </c>
+      <c r="G156" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="157" spans="1:7">
       <c r="A157" s="2" t="s">
         <v>167</v>
       </c>
@@ -4276,11 +4759,14 @@
         <v>8</v>
       </c>
       <c r="D157" s="2"/>
-      <c r="F157" s="7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="158" spans="1:6">
+      <c r="F157" s="5">
+        <v>0</v>
+      </c>
+      <c r="G157" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="158" spans="1:7">
       <c r="A158" s="2" t="s">
         <v>168</v>
       </c>
@@ -4293,11 +4779,14 @@
       <c r="D158" s="2" t="s">
         <v>260</v>
       </c>
-      <c r="F158" s="7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="159" spans="1:6">
+      <c r="F158" s="5">
+        <v>0</v>
+      </c>
+      <c r="G158" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="159" spans="1:7">
       <c r="A159" s="2" t="s">
         <v>169</v>
       </c>
@@ -4310,11 +4799,14 @@
       <c r="D159" s="2" t="s">
         <v>261</v>
       </c>
-      <c r="F159" s="7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="160" spans="1:6">
+      <c r="F159" s="5">
+        <v>0</v>
+      </c>
+      <c r="G159" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="160" spans="1:7">
       <c r="A160" s="2" t="s">
         <v>170</v>
       </c>
@@ -4327,11 +4819,14 @@
       <c r="D160" s="2" t="s">
         <v>262</v>
       </c>
-      <c r="F160" s="7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="161" spans="1:6">
+      <c r="F160" s="5">
+        <v>0</v>
+      </c>
+      <c r="G160" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="161" spans="1:7">
       <c r="A161" s="2" t="s">
         <v>171</v>
       </c>
@@ -4344,11 +4839,14 @@
       <c r="D161" s="2" t="s">
         <v>263</v>
       </c>
-      <c r="F161" s="7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="162" spans="1:6">
+      <c r="F161" s="5">
+        <v>0</v>
+      </c>
+      <c r="G161" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="162" spans="1:7">
       <c r="A162" s="2" t="s">
         <v>172</v>
       </c>
@@ -4361,11 +4859,14 @@
       <c r="D162" s="2" t="s">
         <v>264</v>
       </c>
-      <c r="F162" s="7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="163" spans="1:6">
+      <c r="F162" s="5">
+        <v>0</v>
+      </c>
+      <c r="G162" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="163" spans="1:7">
       <c r="A163" s="2" t="s">
         <v>173</v>
       </c>
@@ -4376,11 +4877,14 @@
         <v>8</v>
       </c>
       <c r="D163" s="2"/>
-      <c r="F163" s="7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="164" spans="1:6" hidden="1">
+      <c r="F163" s="5">
+        <v>0</v>
+      </c>
+      <c r="G163" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="164" spans="1:7">
       <c r="A164" s="2" t="s">
         <v>174</v>
       </c>
@@ -4394,11 +4898,14 @@
       <c r="E164" s="5" t="s">
         <v>298</v>
       </c>
-      <c r="F164" s="7">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="165" spans="1:6" hidden="1">
+      <c r="F164" s="5">
+        <v>0</v>
+      </c>
+      <c r="G164" s="7">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="165" spans="1:7">
       <c r="A165" s="2" t="s">
         <v>175</v>
       </c>
@@ -4412,11 +4919,14 @@
       <c r="E165" s="5" t="s">
         <v>298</v>
       </c>
-      <c r="F165" s="7">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="166" spans="1:6" hidden="1">
+      <c r="F165" s="5">
+        <v>0</v>
+      </c>
+      <c r="G165" s="7">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="166" spans="1:7">
       <c r="A166" s="2" t="s">
         <v>176</v>
       </c>
@@ -4430,11 +4940,14 @@
       <c r="E166" s="5" t="s">
         <v>298</v>
       </c>
-      <c r="F166" s="7">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="167" spans="1:6" hidden="1">
+      <c r="F166" s="5">
+        <v>0</v>
+      </c>
+      <c r="G166" s="7">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="167" spans="1:7">
       <c r="A167" s="2" t="s">
         <v>177</v>
       </c>
@@ -4448,11 +4961,14 @@
       <c r="E167" s="5" t="s">
         <v>298</v>
       </c>
-      <c r="F167" s="7">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="168" spans="1:6" hidden="1">
+      <c r="F167" s="5">
+        <v>0</v>
+      </c>
+      <c r="G167" s="7">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="168" spans="1:7">
       <c r="A168" s="2" t="s">
         <v>178</v>
       </c>
@@ -4466,11 +4982,14 @@
       <c r="E168" s="5" t="s">
         <v>298</v>
       </c>
-      <c r="F168" s="7">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="169" spans="1:6" hidden="1">
+      <c r="F168" s="5">
+        <v>0</v>
+      </c>
+      <c r="G168" s="7">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="169" spans="1:7">
       <c r="A169" s="2" t="s">
         <v>179</v>
       </c>
@@ -4484,11 +5003,14 @@
       <c r="E169" s="5" t="s">
         <v>298</v>
       </c>
-      <c r="F169" s="7">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="170" spans="1:6" hidden="1">
+      <c r="F169" s="5">
+        <v>0</v>
+      </c>
+      <c r="G169" s="7">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="170" spans="1:7">
       <c r="A170" s="2" t="s">
         <v>180</v>
       </c>
@@ -4502,11 +5024,14 @@
       <c r="E170" s="5" t="s">
         <v>298</v>
       </c>
-      <c r="F170" s="7">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="171" spans="1:6" hidden="1">
+      <c r="F170" s="5">
+        <v>0</v>
+      </c>
+      <c r="G170" s="7">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="171" spans="1:7">
       <c r="A171" s="2" t="s">
         <v>181</v>
       </c>
@@ -4520,11 +5045,14 @@
       <c r="E171" s="5" t="s">
         <v>298</v>
       </c>
-      <c r="F171" s="7">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="172" spans="1:6" hidden="1">
+      <c r="F171" s="5">
+        <v>0</v>
+      </c>
+      <c r="G171" s="7">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="172" spans="1:7">
       <c r="A172" s="2" t="s">
         <v>182</v>
       </c>
@@ -4538,11 +5066,14 @@
       <c r="E172" s="5" t="s">
         <v>298</v>
       </c>
-      <c r="F172" s="7">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="173" spans="1:6" hidden="1">
+      <c r="F172" s="5">
+        <v>0</v>
+      </c>
+      <c r="G172" s="7">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="173" spans="1:7">
       <c r="A173" s="2" t="s">
         <v>183</v>
       </c>
@@ -4556,11 +5087,14 @@
       <c r="E173" s="5" t="s">
         <v>298</v>
       </c>
-      <c r="F173" s="7">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="174" spans="1:6" hidden="1">
+      <c r="F173" s="5">
+        <v>0</v>
+      </c>
+      <c r="G173" s="7">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="174" spans="1:7">
       <c r="A174" s="2" t="s">
         <v>184</v>
       </c>
@@ -4574,11 +5108,14 @@
       <c r="E174" s="5" t="s">
         <v>298</v>
       </c>
-      <c r="F174" s="7">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="175" spans="1:6" hidden="1">
+      <c r="F174" s="5">
+        <v>0</v>
+      </c>
+      <c r="G174" s="7">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="175" spans="1:7">
       <c r="A175" s="2" t="s">
         <v>185</v>
       </c>
@@ -4592,11 +5129,14 @@
       <c r="E175" s="5" t="s">
         <v>298</v>
       </c>
-      <c r="F175" s="7">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="176" spans="1:6" hidden="1">
+      <c r="F175" s="5">
+        <v>0</v>
+      </c>
+      <c r="G175" s="7">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="176" spans="1:7">
       <c r="A176" s="2" t="s">
         <v>186</v>
       </c>
@@ -4610,11 +5150,14 @@
       <c r="E176" s="5" t="s">
         <v>298</v>
       </c>
-      <c r="F176" s="7">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="177" spans="1:7" hidden="1">
+      <c r="F176" s="5">
+        <v>0</v>
+      </c>
+      <c r="G176" s="7">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="177" spans="1:8">
       <c r="A177" s="2" t="s">
         <v>187</v>
       </c>
@@ -4628,11 +5171,14 @@
       <c r="E177" s="5" t="s">
         <v>298</v>
       </c>
-      <c r="F177" s="7">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="178" spans="1:7" hidden="1">
+      <c r="F177" s="5">
+        <v>0</v>
+      </c>
+      <c r="G177" s="7">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="178" spans="1:8">
       <c r="A178" s="2" t="s">
         <v>188</v>
       </c>
@@ -4646,11 +5192,14 @@
       <c r="E178" s="5" t="s">
         <v>298</v>
       </c>
-      <c r="F178" s="7">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="179" spans="1:7">
+      <c r="F178" s="5">
+        <v>0</v>
+      </c>
+      <c r="G178" s="7">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="179" spans="1:8">
       <c r="A179" s="2" t="s">
         <v>189</v>
       </c>
@@ -4661,12 +5210,15 @@
         <v>123</v>
       </c>
       <c r="D179" s="2"/>
-      <c r="F179" s="7">
-        <v>1</v>
-      </c>
-      <c r="G179" s="4"/>
-    </row>
-    <row r="180" spans="1:7">
+      <c r="F179" s="5">
+        <v>0</v>
+      </c>
+      <c r="G179" s="7">
+        <v>1</v>
+      </c>
+      <c r="H179" s="4"/>
+    </row>
+    <row r="180" spans="1:8">
       <c r="A180" s="2" t="s">
         <v>190</v>
       </c>
@@ -4677,12 +5229,15 @@
         <v>123</v>
       </c>
       <c r="D180" s="2"/>
-      <c r="F180" s="7">
-        <v>1</v>
-      </c>
-      <c r="G180" s="4"/>
-    </row>
-    <row r="181" spans="1:7">
+      <c r="F180" s="5">
+        <v>0</v>
+      </c>
+      <c r="G180" s="7">
+        <v>1</v>
+      </c>
+      <c r="H180" s="4"/>
+    </row>
+    <row r="181" spans="1:8">
       <c r="A181" s="2" t="s">
         <v>191</v>
       </c>
@@ -4693,12 +5248,15 @@
         <v>123</v>
       </c>
       <c r="D181" s="2"/>
-      <c r="F181" s="7">
-        <v>1</v>
-      </c>
-      <c r="G181" s="4"/>
-    </row>
-    <row r="182" spans="1:7">
+      <c r="F181" s="5">
+        <v>0</v>
+      </c>
+      <c r="G181" s="7">
+        <v>1</v>
+      </c>
+      <c r="H181" s="4"/>
+    </row>
+    <row r="182" spans="1:8">
       <c r="A182" s="2" t="s">
         <v>192</v>
       </c>
@@ -4709,12 +5267,15 @@
         <v>123</v>
       </c>
       <c r="D182" s="2"/>
-      <c r="F182" s="7">
-        <v>1</v>
-      </c>
-      <c r="G182" s="4"/>
-    </row>
-    <row r="183" spans="1:7">
+      <c r="F182" s="5">
+        <v>0</v>
+      </c>
+      <c r="G182" s="7">
+        <v>1</v>
+      </c>
+      <c r="H182" s="4"/>
+    </row>
+    <row r="183" spans="1:8">
       <c r="A183" s="2" t="s">
         <v>193</v>
       </c>
@@ -4725,12 +5286,15 @@
         <v>123</v>
       </c>
       <c r="D183" s="2"/>
-      <c r="F183" s="7">
-        <v>1</v>
-      </c>
-      <c r="G183" s="4"/>
-    </row>
-    <row r="184" spans="1:7">
+      <c r="F183" s="5">
+        <v>0</v>
+      </c>
+      <c r="G183" s="7">
+        <v>1</v>
+      </c>
+      <c r="H183" s="4"/>
+    </row>
+    <row r="184" spans="1:8">
       <c r="A184" s="2" t="s">
         <v>194</v>
       </c>
@@ -4741,12 +5305,15 @@
         <v>123</v>
       </c>
       <c r="D184" s="2"/>
-      <c r="F184" s="7">
-        <v>1</v>
-      </c>
-      <c r="G184" s="4"/>
-    </row>
-    <row r="185" spans="1:7">
+      <c r="F184" s="5">
+        <v>0</v>
+      </c>
+      <c r="G184" s="7">
+        <v>1</v>
+      </c>
+      <c r="H184" s="4"/>
+    </row>
+    <row r="185" spans="1:8">
       <c r="A185" s="2" t="s">
         <v>195</v>
       </c>
@@ -4757,12 +5324,15 @@
         <v>123</v>
       </c>
       <c r="D185" s="2"/>
-      <c r="F185" s="7">
-        <v>1</v>
-      </c>
-      <c r="G185" s="4"/>
-    </row>
-    <row r="186" spans="1:7">
+      <c r="F185" s="5">
+        <v>0</v>
+      </c>
+      <c r="G185" s="7">
+        <v>1</v>
+      </c>
+      <c r="H185" s="4"/>
+    </row>
+    <row r="186" spans="1:8">
       <c r="A186" s="2" t="s">
         <v>196</v>
       </c>
@@ -4773,12 +5343,15 @@
         <v>123</v>
       </c>
       <c r="D186" s="2"/>
-      <c r="F186" s="7">
-        <v>1</v>
-      </c>
-      <c r="G186" s="4"/>
-    </row>
-    <row r="187" spans="1:7">
+      <c r="F186" s="5">
+        <v>0</v>
+      </c>
+      <c r="G186" s="7">
+        <v>1</v>
+      </c>
+      <c r="H186" s="4"/>
+    </row>
+    <row r="187" spans="1:8">
       <c r="A187" s="3" t="s">
         <v>197</v>
       </c>
@@ -4791,11 +5364,14 @@
       <c r="D187" s="2" t="s">
         <v>265</v>
       </c>
-      <c r="F187" s="7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="188" spans="1:7">
+      <c r="F187" s="5">
+        <v>0</v>
+      </c>
+      <c r="G187" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="188" spans="1:8">
       <c r="A188" s="2" t="s">
         <v>198</v>
       </c>
@@ -4808,11 +5384,14 @@
       <c r="D188" s="2" t="s">
         <v>266</v>
       </c>
-      <c r="F188" s="7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="189" spans="1:7">
+      <c r="F188" s="5">
+        <v>0</v>
+      </c>
+      <c r="G188" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="189" spans="1:8">
       <c r="A189" s="2" t="s">
         <v>199</v>
       </c>
@@ -4825,11 +5404,14 @@
       <c r="D189" s="2" t="s">
         <v>267</v>
       </c>
-      <c r="F189" s="7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="190" spans="1:7">
+      <c r="F189" s="5">
+        <v>0</v>
+      </c>
+      <c r="G189" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="190" spans="1:8">
       <c r="A190" s="2" t="s">
         <v>200</v>
       </c>
@@ -4840,11 +5422,14 @@
         <v>8</v>
       </c>
       <c r="D190" s="2"/>
-      <c r="F190" s="7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="191" spans="1:7">
+      <c r="F190" s="5">
+        <v>0</v>
+      </c>
+      <c r="G190" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="191" spans="1:8">
       <c r="A191" s="3" t="s">
         <v>201</v>
       </c>
@@ -4860,11 +5445,14 @@
       <c r="E191" s="2" t="s">
         <v>275</v>
       </c>
-      <c r="F191" s="7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="192" spans="1:7">
+      <c r="F191" s="5">
+        <v>0</v>
+      </c>
+      <c r="G191" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="192" spans="1:8">
       <c r="A192" s="2" t="s">
         <v>202</v>
       </c>
@@ -4875,11 +5463,14 @@
         <v>8</v>
       </c>
       <c r="D192" s="2"/>
-      <c r="F192" s="7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="193" spans="1:7">
+      <c r="F192" s="5">
+        <v>0</v>
+      </c>
+      <c r="G192" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="193" spans="1:8">
       <c r="A193" s="3" t="s">
         <v>203</v>
       </c>
@@ -4895,11 +5486,14 @@
       <c r="E193" s="5" t="s">
         <v>285</v>
       </c>
-      <c r="F193" s="7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="194" spans="1:7">
+      <c r="F193" s="5">
+        <v>0</v>
+      </c>
+      <c r="G193" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="194" spans="1:8">
       <c r="A194" s="2" t="s">
         <v>204</v>
       </c>
@@ -4910,12 +5504,15 @@
         <v>8</v>
       </c>
       <c r="D194" s="2"/>
-      <c r="F194" s="7">
-        <v>1</v>
-      </c>
-      <c r="G194" s="4"/>
-    </row>
-    <row r="195" spans="1:7">
+      <c r="F194" s="5">
+        <v>0</v>
+      </c>
+      <c r="G194" s="7">
+        <v>1</v>
+      </c>
+      <c r="H194" s="4"/>
+    </row>
+    <row r="195" spans="1:8">
       <c r="A195" s="2" t="s">
         <v>205</v>
       </c>
@@ -4926,12 +5523,15 @@
         <v>8</v>
       </c>
       <c r="D195" s="2"/>
-      <c r="F195" s="7">
-        <v>1</v>
-      </c>
-      <c r="G195" s="4"/>
-    </row>
-    <row r="196" spans="1:7" hidden="1">
+      <c r="F195" s="5">
+        <v>0</v>
+      </c>
+      <c r="G195" s="7">
+        <v>1</v>
+      </c>
+      <c r="H195" s="4"/>
+    </row>
+    <row r="196" spans="1:8">
       <c r="A196" s="2" t="s">
         <v>206</v>
       </c>
@@ -4945,14 +5545,17 @@
       <c r="E196" s="5" t="s">
         <v>285</v>
       </c>
-      <c r="F196" s="7">
+      <c r="F196" s="5">
+        <v>1</v>
+      </c>
+      <c r="G196" s="7">
         <v>2</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="G24:G26"/>
-    <mergeCell ref="G68:G69"/>
+    <mergeCell ref="H24:H26"/>
+    <mergeCell ref="H68:H69"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
